--- a/backend/LPG testing/upload-{model}.xlsx
+++ b/backend/LPG testing/upload-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1747358-A051-42A3-84BC-E0DC8B2F41A3}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2AA26B1-513C-4605-8266-51FD89385BA5}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carbon Credits" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="20">
   <si>
     <t>Units</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>CO2 emited - {model} scenario</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Inputs</t>
@@ -579,13 +576,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>3</v>
+      <c r="C1" s="6">
+        <v>2020</v>
       </c>
       <c r="D1" s="6">
         <v>2021</v>
@@ -918,16 +915,16 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
+      <c r="D1" s="6">
+        <v>2020</v>
       </c>
       <c r="E1" s="6">
         <v>2021</v>
@@ -1052,13 +1049,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="10">
         <v>0</v>
@@ -1186,13 +1183,13 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="10">
         <v>0</v>
@@ -1320,13 +1317,13 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="10">
         <v>0</v>
@@ -1454,147 +1451,147 @@
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1722,13 +1719,13 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="10">
         <v>0</v>
@@ -1856,13 +1853,13 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
@@ -1990,147 +1987,147 @@
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="19">
         <v>0</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -2258,13 +2255,13 @@
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2392,147 +2389,147 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="10">
         <v>0</v>
@@ -2660,13 +2657,13 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="10">
         <v>0</v>
@@ -2794,13 +2791,13 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
@@ -2928,136 +2925,136 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="19">
         <v>0</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3075,13 +3072,13 @@
   <sheetData>
     <row r="1" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>3</v>
+      <c r="C1" s="6">
+        <v>2020</v>
       </c>
       <c r="D1" s="6">
         <v>2021</v>
@@ -3206,10 +3203,10 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -3337,10 +3334,10 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="10">
         <v>0</v>
@@ -3468,10 +3465,10 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="10">
         <v>0</v>
@@ -3599,141 +3596,141 @@
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -3861,10 +3858,10 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
@@ -3992,10 +3989,10 @@
     </row>
     <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -4123,133 +4120,133 @@
     </row>
     <row r="9" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
